--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260612.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,505,027</t>
+          <t>42,460,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.35%</t>
+          <t>64.42%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,561,703</t>
+          <t>2,558,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>7.02%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,252,000</t>
+          <t>21,230,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,716,267</t>
+          <t>5,710,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,309,286</t>
+          <t>20,288,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>499,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,705,608</t>
+          <t>2,702,608</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,324,901</t>
+          <t>2,321,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,598,285</t>
+          <t>4,593,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -831,56 +831,56 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,189,617</t>
+          <t>1,188,617</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>180,515</t>
+          <t>5,431,296</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,437,296</t>
+          <t>180,515</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,330,520</t>
+          <t>5,324,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -946,68 +946,68 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,385,000</t>
+          <t>1,955,288</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>3,381,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,22 +1019,22 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1051,34 +1051,34 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,273,000</t>
+          <t>1,272,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,957,288</t>
+          <t>167,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>12,818,134</t>
+          <t>12,804,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1139,78 +1139,78 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>138,921</t>
+          <t>137,921</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>847,349</t>
+          <t>146,499</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>146,499</t>
+          <t>1,893,321</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,895,321</t>
+          <t>846,349</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1227,117 +1227,117 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,002,822</t>
+          <t>1,001,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,728,000</t>
+          <t>3,066,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,070,000</t>
+          <t>1,726,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,201,441</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>1,202,441</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>779,000</t>
+          <t>5,610,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>799,897</t>
+          <t>778,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,61 +1371,61 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,537,384</t>
+          <t>798,897</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5,616,000</t>
+          <t>563,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>563,000</t>
+          <t>1,535,384</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,39 +1437,39 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,355,981</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>938,659</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,39 +1481,39 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>939,659</t>
+          <t>3,351,981</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>4,480,578</t>
+          <t>371,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>4,475,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,578,703</t>
+          <t>2,575,703</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,357,249</t>
+          <t>7,349,249</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>10,392,121</t>
+          <t>10,381,121</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,134,107</t>
+          <t>2,132,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>5,020,956</t>
+          <t>5,015,956</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,189,076</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>829,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>1,187,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>91,000</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,545,400</t>
+          <t>1,008,121</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>1,543,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,009,121</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,725,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,39 +1943,39 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>788,000</t>
+          <t>1,723,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>787,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>693,000</t>
+          <t>692,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>486,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>486,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>651,288,348</t>
+          <t>630,274,095</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -2081,10 +2081,28 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>360,024,894</t>
+          <t>389,628,894</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>PFUR_NTD</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>178,435,164</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
